--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260612.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260612.xlsx
@@ -953,17 +953,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>490,863,839</t>
+          <t>232,733,341</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -975,17 +975,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>232,733,341</t>
+          <t>490,863,839</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>337,149,832</t>
+          <t>270,666,697</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>270,666,697</t>
+          <t>337,149,832</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>198,532,483</t>
+          <t>231,566,464</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>231,566,464</t>
+          <t>198,532,483</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
